--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216464</v>
+        <v>121216488</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511871</v>
+        <v>511890</v>
       </c>
       <c r="R2" t="n">
-        <v>6734288</v>
+        <v>6734232</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216472</v>
+        <v>121216485</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>100347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511926</v>
+        <v>511856</v>
       </c>
       <c r="R3" t="n">
-        <v>6734295</v>
+        <v>6734258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216460</v>
+        <v>121216474</v>
       </c>
       <c r="B4" t="n">
-        <v>91127</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,34 +895,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511913</v>
+        <v>511908</v>
       </c>
       <c r="R4" t="n">
-        <v>6734224</v>
+        <v>6734282</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216490</v>
+        <v>121216473</v>
       </c>
       <c r="B5" t="n">
-        <v>100337</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,38 +1002,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511875</v>
+        <v>511888</v>
       </c>
       <c r="R5" t="n">
-        <v>6734249</v>
+        <v>6734296</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216465</v>
+        <v>121216478</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511882</v>
+        <v>511932</v>
       </c>
       <c r="R6" t="n">
-        <v>6734284</v>
+        <v>6734295</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216466</v>
+        <v>121216490</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>100347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,47 +1224,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511896</v>
+        <v>511875</v>
       </c>
       <c r="R7" t="n">
-        <v>6734295</v>
+        <v>6734249</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216469</v>
+        <v>121216462</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>90983</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,47 +1326,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511918</v>
+        <v>511910</v>
       </c>
       <c r="R8" t="n">
-        <v>6734258</v>
+        <v>6734222</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216482</v>
+        <v>121216461</v>
       </c>
       <c r="B9" t="n">
-        <v>98071</v>
+        <v>91137</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,43 +1432,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511946</v>
+        <v>511887</v>
       </c>
       <c r="R9" t="n">
-        <v>6734303</v>
+        <v>6734253</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216488</v>
+        <v>121216472</v>
       </c>
       <c r="B10" t="n">
-        <v>100337</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,38 +1530,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511890</v>
+        <v>511926</v>
       </c>
       <c r="R10" t="n">
-        <v>6734232</v>
+        <v>6734295</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216454</v>
+        <v>121216489</v>
       </c>
       <c r="B11" t="n">
-        <v>90687</v>
+        <v>100347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511885</v>
+        <v>511874</v>
       </c>
       <c r="R11" t="n">
-        <v>6734256</v>
+        <v>6734258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216474</v>
+        <v>121216482</v>
       </c>
       <c r="B12" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,7 +1766,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1798,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511908</v>
+        <v>511946</v>
       </c>
       <c r="R12" t="n">
-        <v>6734282</v>
+        <v>6734303</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216455</v>
+        <v>121216466</v>
       </c>
       <c r="B13" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,38 +1854,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511912</v>
+        <v>511896</v>
       </c>
       <c r="R13" t="n">
-        <v>6734222</v>
+        <v>6734295</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216456</v>
+        <v>121216468</v>
       </c>
       <c r="B14" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,38 +1965,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511887</v>
+        <v>511953</v>
       </c>
       <c r="R14" t="n">
-        <v>6734253</v>
+        <v>6734306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216467</v>
+        <v>121216486</v>
       </c>
       <c r="B15" t="n">
-        <v>98071</v>
+        <v>100347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,47 +2076,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511936</v>
+        <v>511930</v>
       </c>
       <c r="R15" t="n">
-        <v>6734297</v>
+        <v>6734223</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216486</v>
+        <v>121216481</v>
       </c>
       <c r="B16" t="n">
-        <v>100337</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,38 +2178,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511930</v>
+        <v>511892</v>
       </c>
       <c r="R16" t="n">
-        <v>6734223</v>
+        <v>6734294</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216476</v>
+        <v>121216475</v>
       </c>
       <c r="B17" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511926</v>
+        <v>511912</v>
       </c>
       <c r="R17" t="n">
-        <v>6734268</v>
+        <v>6734269</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,10 +2388,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216479</v>
+        <v>121216483</v>
       </c>
       <c r="B18" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511944</v>
+        <v>511919</v>
       </c>
       <c r="R18" t="n">
-        <v>6734302</v>
+        <v>6734255</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,10 +2499,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216489</v>
+        <v>121216477</v>
       </c>
       <c r="B19" t="n">
-        <v>100337</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2511,28 +2511,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
@@ -2542,7 +2551,7 @@
         <v>511874</v>
       </c>
       <c r="R19" t="n">
-        <v>6734258</v>
+        <v>6734290</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216462</v>
+        <v>121216487</v>
       </c>
       <c r="B20" t="n">
-        <v>90973</v>
+        <v>100347</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2613,25 +2622,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2641,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511910</v>
+        <v>511896</v>
       </c>
       <c r="R20" t="n">
-        <v>6734222</v>
+        <v>6734236</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216463</v>
+        <v>121216479</v>
       </c>
       <c r="B21" t="n">
-        <v>90973</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,38 +2724,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511882</v>
+        <v>511944</v>
       </c>
       <c r="R21" t="n">
-        <v>6734252</v>
+        <v>6734302</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,10 +2823,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216483</v>
+        <v>121216463</v>
       </c>
       <c r="B22" t="n">
-        <v>98071</v>
+        <v>90983</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,47 +2835,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511919</v>
+        <v>511882</v>
       </c>
       <c r="R22" t="n">
-        <v>6734255</v>
+        <v>6734252</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2916,10 +2925,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216478</v>
+        <v>121216465</v>
       </c>
       <c r="B23" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2951,7 +2960,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2965,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511932</v>
+        <v>511882</v>
       </c>
       <c r="R23" t="n">
-        <v>6734295</v>
+        <v>6734284</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,10 +3036,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216471</v>
+        <v>121216476</v>
       </c>
       <c r="B24" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3062,7 +3071,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3076,10 +3085,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511918</v>
+        <v>511926</v>
       </c>
       <c r="R24" t="n">
-        <v>6734292</v>
+        <v>6734268</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3138,10 +3147,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216473</v>
+        <v>121216455</v>
       </c>
       <c r="B25" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,47 +3159,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511888</v>
+        <v>511912</v>
       </c>
       <c r="R25" t="n">
-        <v>6734296</v>
+        <v>6734222</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216485</v>
+        <v>121216460</v>
       </c>
       <c r="B26" t="n">
-        <v>100337</v>
+        <v>91137</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3261,25 +3261,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511856</v>
+        <v>511913</v>
       </c>
       <c r="R26" t="n">
-        <v>6734258</v>
+        <v>6734224</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216468</v>
+        <v>121216467</v>
       </c>
       <c r="B27" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511953</v>
+        <v>511936</v>
       </c>
       <c r="R27" t="n">
-        <v>6734306</v>
+        <v>6734297</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216477</v>
+        <v>121216480</v>
       </c>
       <c r="B28" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511874</v>
+        <v>511859</v>
       </c>
       <c r="R28" t="n">
-        <v>6734290</v>
+        <v>6734287</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216487</v>
+        <v>121216471</v>
       </c>
       <c r="B29" t="n">
-        <v>100337</v>
+        <v>98081</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3585,38 +3585,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511896</v>
+        <v>511918</v>
       </c>
       <c r="R29" t="n">
-        <v>6734236</v>
+        <v>6734292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,10 +3684,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216480</v>
+        <v>121216456</v>
       </c>
       <c r="B30" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3687,47 +3696,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511859</v>
+        <v>511887</v>
       </c>
       <c r="R30" t="n">
-        <v>6734287</v>
+        <v>6734253</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,10 +3786,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216481</v>
+        <v>121216454</v>
       </c>
       <c r="B31" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3798,47 +3798,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511892</v>
+        <v>511885</v>
       </c>
       <c r="R31" t="n">
-        <v>6734294</v>
+        <v>6734256</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3897,10 +3888,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216475</v>
+        <v>121216469</v>
       </c>
       <c r="B32" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3932,7 +3923,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3946,10 +3937,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511912</v>
+        <v>511918</v>
       </c>
       <c r="R32" t="n">
-        <v>6734269</v>
+        <v>6734258</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4008,10 +3999,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216461</v>
+        <v>121216464</v>
       </c>
       <c r="B33" t="n">
-        <v>91127</v>
+        <v>98081</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4024,34 +4015,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511887</v>
+        <v>511871</v>
       </c>
       <c r="R33" t="n">
-        <v>6734253</v>
+        <v>6734288</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216488</v>
+        <v>121216474</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511890</v>
+        <v>511908</v>
       </c>
       <c r="R2" t="n">
-        <v>6734232</v>
+        <v>6734282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216485</v>
+        <v>121216488</v>
       </c>
       <c r="B3" t="n">
         <v>100347</v>
@@ -817,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511856</v>
+        <v>511890</v>
       </c>
       <c r="R3" t="n">
-        <v>6734258</v>
+        <v>6734232</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216474</v>
+        <v>121216485</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>100347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,47 +900,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511908</v>
+        <v>511856</v>
       </c>
       <c r="R4" t="n">
-        <v>6734282</v>
+        <v>6734258</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216490</v>
+        <v>121216462</v>
       </c>
       <c r="B7" t="n">
-        <v>100347</v>
+        <v>90983</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511875</v>
+        <v>511910</v>
       </c>
       <c r="R7" t="n">
-        <v>6734249</v>
+        <v>6734222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216462</v>
+        <v>121216490</v>
       </c>
       <c r="B8" t="n">
-        <v>90983</v>
+        <v>100347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511910</v>
+        <v>511875</v>
       </c>
       <c r="R8" t="n">
-        <v>6734222</v>
+        <v>6734249</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216474</v>
+        <v>121216488</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511908</v>
+        <v>511890</v>
       </c>
       <c r="R2" t="n">
-        <v>6734282</v>
+        <v>6734232</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216488</v>
+        <v>121216485</v>
       </c>
       <c r="B3" t="n">
         <v>100347</v>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511890</v>
+        <v>511856</v>
       </c>
       <c r="R3" t="n">
-        <v>6734232</v>
+        <v>6734258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216485</v>
+        <v>121216474</v>
       </c>
       <c r="B4" t="n">
-        <v>100347</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +891,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511856</v>
+        <v>511908</v>
       </c>
       <c r="R4" t="n">
-        <v>6734258</v>
+        <v>6734282</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216462</v>
+        <v>121216490</v>
       </c>
       <c r="B7" t="n">
-        <v>90983</v>
+        <v>100347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1224,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511910</v>
+        <v>511875</v>
       </c>
       <c r="R7" t="n">
-        <v>6734222</v>
+        <v>6734249</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216490</v>
+        <v>121216462</v>
       </c>
       <c r="B8" t="n">
-        <v>100347</v>
+        <v>90983</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511875</v>
+        <v>511910</v>
       </c>
       <c r="R8" t="n">
-        <v>6734249</v>
+        <v>6734222</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216455</v>
+        <v>121216467</v>
       </c>
       <c r="B25" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3159,38 +3159,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511912</v>
+        <v>511936</v>
       </c>
       <c r="R25" t="n">
-        <v>6734222</v>
+        <v>6734297</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,10 +3258,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216460</v>
+        <v>121216480</v>
       </c>
       <c r="B26" t="n">
-        <v>91137</v>
+        <v>98081</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3265,34 +3274,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511913</v>
+        <v>511859</v>
       </c>
       <c r="R26" t="n">
-        <v>6734224</v>
+        <v>6734287</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3351,10 +3369,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216467</v>
+        <v>121216455</v>
       </c>
       <c r="B27" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3363,47 +3381,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511936</v>
+        <v>511912</v>
       </c>
       <c r="R27" t="n">
-        <v>6734297</v>
+        <v>6734222</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216480</v>
+        <v>121216460</v>
       </c>
       <c r="B28" t="n">
-        <v>98081</v>
+        <v>91137</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3478,43 +3487,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511859</v>
+        <v>511913</v>
       </c>
       <c r="R28" t="n">
-        <v>6734287</v>
+        <v>6734224</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216488</v>
+        <v>121216461</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>91137</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511890</v>
+        <v>511887</v>
       </c>
       <c r="R2" t="n">
-        <v>6734232</v>
+        <v>6734253</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216485</v>
+        <v>121216466</v>
       </c>
       <c r="B3" t="n">
-        <v>100347</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511856</v>
+        <v>511896</v>
       </c>
       <c r="R3" t="n">
-        <v>6734258</v>
+        <v>6734295</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216474</v>
+        <v>121216467</v>
       </c>
       <c r="B4" t="n">
         <v>98081</v>
@@ -914,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -928,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511908</v>
+        <v>511936</v>
       </c>
       <c r="R4" t="n">
-        <v>6734282</v>
+        <v>6734297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216473</v>
+        <v>121216454</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,47 +1011,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511888</v>
+        <v>511885</v>
       </c>
       <c r="R5" t="n">
-        <v>6734296</v>
+        <v>6734256</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216478</v>
+        <v>121216465</v>
       </c>
       <c r="B6" t="n">
         <v>98081</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511932</v>
+        <v>511882</v>
       </c>
       <c r="R6" t="n">
-        <v>6734295</v>
+        <v>6734284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216490</v>
+        <v>121216476</v>
       </c>
       <c r="B7" t="n">
-        <v>100347</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,38 +1224,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511875</v>
+        <v>511926</v>
       </c>
       <c r="R7" t="n">
-        <v>6734249</v>
+        <v>6734268</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216462</v>
+        <v>121216479</v>
       </c>
       <c r="B8" t="n">
-        <v>90983</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,38 +1335,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511910</v>
+        <v>511944</v>
       </c>
       <c r="R8" t="n">
-        <v>6734222</v>
+        <v>6734302</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216461</v>
+        <v>121216487</v>
       </c>
       <c r="B9" t="n">
-        <v>91137</v>
+        <v>100347</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,25 +1446,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1456,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511887</v>
+        <v>511896</v>
       </c>
       <c r="R9" t="n">
-        <v>6734253</v>
+        <v>6734236</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216472</v>
+        <v>121216478</v>
       </c>
       <c r="B10" t="n">
         <v>98081</v>
@@ -1553,7 +1571,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1567,7 +1585,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511926</v>
+        <v>511932</v>
       </c>
       <c r="R10" t="n">
         <v>6734295</v>
@@ -1629,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216489</v>
+        <v>121216455</v>
       </c>
       <c r="B11" t="n">
-        <v>100347</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1659,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511874</v>
+        <v>511912</v>
       </c>
       <c r="R11" t="n">
-        <v>6734258</v>
+        <v>6734222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,7 +1749,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216482</v>
+        <v>121216475</v>
       </c>
       <c r="B12" t="n">
         <v>98081</v>
@@ -1766,7 +1784,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1780,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511946</v>
+        <v>511912</v>
       </c>
       <c r="R12" t="n">
-        <v>6734303</v>
+        <v>6734269</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216466</v>
+        <v>121216463</v>
       </c>
       <c r="B13" t="n">
-        <v>98081</v>
+        <v>90983</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,47 +1872,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511896</v>
+        <v>511882</v>
       </c>
       <c r="R13" t="n">
-        <v>6734295</v>
+        <v>6734252</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2064,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216486</v>
+        <v>121216483</v>
       </c>
       <c r="B15" t="n">
-        <v>100347</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,38 +2085,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511930</v>
+        <v>511919</v>
       </c>
       <c r="R15" t="n">
-        <v>6734223</v>
+        <v>6734255</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216481</v>
+        <v>121216460</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>91137</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2182,43 +2200,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511892</v>
+        <v>511913</v>
       </c>
       <c r="R16" t="n">
-        <v>6734294</v>
+        <v>6734224</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216475</v>
+        <v>121216473</v>
       </c>
       <c r="B17" t="n">
         <v>98081</v>
@@ -2326,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511912</v>
+        <v>511888</v>
       </c>
       <c r="R17" t="n">
-        <v>6734269</v>
+        <v>6734296</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216483</v>
+        <v>121216481</v>
       </c>
       <c r="B18" t="n">
         <v>98081</v>
@@ -2437,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511919</v>
+        <v>511892</v>
       </c>
       <c r="R18" t="n">
-        <v>6734255</v>
+        <v>6734294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,10 +2508,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216477</v>
+        <v>121216490</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>100347</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2511,47 +2520,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511874</v>
+        <v>511875</v>
       </c>
       <c r="R19" t="n">
-        <v>6734290</v>
+        <v>6734249</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216487</v>
+        <v>121216485</v>
       </c>
       <c r="B20" t="n">
         <v>100347</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511896</v>
+        <v>511856</v>
       </c>
       <c r="R20" t="n">
-        <v>6734236</v>
+        <v>6734258</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216479</v>
+        <v>121216456</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,47 +2724,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511944</v>
+        <v>511887</v>
       </c>
       <c r="R21" t="n">
-        <v>6734302</v>
+        <v>6734253</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,10 +2814,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216463</v>
+        <v>121216486</v>
       </c>
       <c r="B22" t="n">
-        <v>90983</v>
+        <v>100347</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2835,25 +2826,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2863,10 +2854,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511882</v>
+        <v>511930</v>
       </c>
       <c r="R22" t="n">
-        <v>6734252</v>
+        <v>6734223</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,10 +2916,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216465</v>
+        <v>121216489</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>100347</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2937,47 +2928,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511882</v>
+        <v>511874</v>
       </c>
       <c r="R23" t="n">
-        <v>6734284</v>
+        <v>6734258</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,7 +3018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216476</v>
+        <v>121216472</v>
       </c>
       <c r="B24" t="n">
         <v>98081</v>
@@ -3071,7 +3053,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3088,7 +3070,7 @@
         <v>511926</v>
       </c>
       <c r="R24" t="n">
-        <v>6734268</v>
+        <v>6734295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,7 +3129,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216467</v>
+        <v>121216464</v>
       </c>
       <c r="B25" t="n">
         <v>98081</v>
@@ -3182,7 +3164,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3196,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511936</v>
+        <v>511871</v>
       </c>
       <c r="R25" t="n">
-        <v>6734297</v>
+        <v>6734288</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,10 +3240,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216480</v>
+        <v>121216488</v>
       </c>
       <c r="B26" t="n">
-        <v>98081</v>
+        <v>100347</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3270,47 +3252,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511859</v>
+        <v>511890</v>
       </c>
       <c r="R26" t="n">
-        <v>6734287</v>
+        <v>6734232</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,10 +3342,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216455</v>
+        <v>121216480</v>
       </c>
       <c r="B27" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3381,38 +3354,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511912</v>
+        <v>511859</v>
       </c>
       <c r="R27" t="n">
-        <v>6734222</v>
+        <v>6734287</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,10 +3453,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216460</v>
+        <v>121216462</v>
       </c>
       <c r="B28" t="n">
-        <v>91137</v>
+        <v>90983</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3483,25 +3465,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3511,10 +3493,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511913</v>
+        <v>511910</v>
       </c>
       <c r="R28" t="n">
-        <v>6734224</v>
+        <v>6734222</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3684,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216456</v>
+        <v>121216482</v>
       </c>
       <c r="B30" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3696,38 +3678,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511887</v>
+        <v>511946</v>
       </c>
       <c r="R30" t="n">
-        <v>6734253</v>
+        <v>6734303</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,10 +3777,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216454</v>
+        <v>121216469</v>
       </c>
       <c r="B31" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3798,38 +3789,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511885</v>
+        <v>511918</v>
       </c>
       <c r="R31" t="n">
-        <v>6734256</v>
+        <v>6734258</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216469</v>
+        <v>121216474</v>
       </c>
       <c r="B32" t="n">
         <v>98081</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511918</v>
+        <v>511908</v>
       </c>
       <c r="R32" t="n">
-        <v>6734258</v>
+        <v>6734282</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216464</v>
+        <v>121216477</v>
       </c>
       <c r="B33" t="n">
         <v>98081</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511871</v>
+        <v>511874</v>
       </c>
       <c r="R33" t="n">
-        <v>6734288</v>
+        <v>6734290</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216478</v>
+        <v>121216455</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,47 +1548,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511932</v>
+        <v>511912</v>
       </c>
       <c r="R10" t="n">
-        <v>6734295</v>
+        <v>6734222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216455</v>
+        <v>121216478</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,38 +1650,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511912</v>
+        <v>511932</v>
       </c>
       <c r="R11" t="n">
-        <v>6734222</v>
+        <v>6734295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216461</v>
+        <v>121216463</v>
       </c>
       <c r="B2" t="n">
-        <v>91137</v>
+        <v>90995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511887</v>
+        <v>511882</v>
       </c>
       <c r="R2" t="n">
-        <v>6734253</v>
+        <v>6734252</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216466</v>
+        <v>121216476</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511896</v>
+        <v>511926</v>
       </c>
       <c r="R3" t="n">
-        <v>6734295</v>
+        <v>6734268</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216467</v>
+        <v>121216456</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,47 +900,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511936</v>
+        <v>511887</v>
       </c>
       <c r="R4" t="n">
-        <v>6734297</v>
+        <v>6734253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216454</v>
+        <v>121216485</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
+        <v>100360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511885</v>
+        <v>511856</v>
       </c>
       <c r="R5" t="n">
-        <v>6734256</v>
+        <v>6734258</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216465</v>
+        <v>121216469</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511882</v>
+        <v>511918</v>
       </c>
       <c r="R6" t="n">
-        <v>6734284</v>
+        <v>6734258</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216476</v>
+        <v>121216489</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>100360</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,47 +1215,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511926</v>
+        <v>511874</v>
       </c>
       <c r="R7" t="n">
-        <v>6734268</v>
+        <v>6734258</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216479</v>
+        <v>121216471</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,7 +1340,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1372,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511944</v>
+        <v>511918</v>
       </c>
       <c r="R8" t="n">
-        <v>6734302</v>
+        <v>6734292</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216487</v>
+        <v>121216477</v>
       </c>
       <c r="B9" t="n">
-        <v>100347</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,38 +1428,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511896</v>
+        <v>511874</v>
       </c>
       <c r="R9" t="n">
-        <v>6734236</v>
+        <v>6734290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216455</v>
+        <v>121216480</v>
       </c>
       <c r="B10" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,38 +1539,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511912</v>
+        <v>511859</v>
       </c>
       <c r="R10" t="n">
-        <v>6734222</v>
+        <v>6734287</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216478</v>
+        <v>121216474</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511932</v>
+        <v>511908</v>
       </c>
       <c r="R11" t="n">
-        <v>6734295</v>
+        <v>6734282</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,7 +1752,7 @@
         <v>121216475</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216463</v>
+        <v>121216490</v>
       </c>
       <c r="B13" t="n">
-        <v>90983</v>
+        <v>100360</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,25 +1872,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511882</v>
+        <v>511875</v>
       </c>
       <c r="R13" t="n">
-        <v>6734252</v>
+        <v>6734249</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216468</v>
+        <v>121216466</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511953</v>
+        <v>511896</v>
       </c>
       <c r="R14" t="n">
-        <v>6734306</v>
+        <v>6734295</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216483</v>
+        <v>121216465</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511919</v>
+        <v>511882</v>
       </c>
       <c r="R15" t="n">
-        <v>6734255</v>
+        <v>6734284</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216460</v>
+        <v>121216482</v>
       </c>
       <c r="B16" t="n">
-        <v>91137</v>
+        <v>98094</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,34 +2200,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511913</v>
+        <v>511946</v>
       </c>
       <c r="R16" t="n">
-        <v>6734224</v>
+        <v>6734303</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216473</v>
+        <v>121216478</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,7 +2330,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2335,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511888</v>
+        <v>511932</v>
       </c>
       <c r="R17" t="n">
-        <v>6734296</v>
+        <v>6734295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216481</v>
+        <v>121216455</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,47 +2418,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511892</v>
+        <v>511912</v>
       </c>
       <c r="R18" t="n">
-        <v>6734294</v>
+        <v>6734222</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216490</v>
+        <v>121216473</v>
       </c>
       <c r="B19" t="n">
-        <v>100347</v>
+        <v>98094</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,38 +2520,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511875</v>
+        <v>511888</v>
       </c>
       <c r="R19" t="n">
-        <v>6734249</v>
+        <v>6734296</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2610,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216485</v>
+        <v>121216481</v>
       </c>
       <c r="B20" t="n">
-        <v>100347</v>
+        <v>98094</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,38 +2631,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511856</v>
+        <v>511892</v>
       </c>
       <c r="R20" t="n">
-        <v>6734258</v>
+        <v>6734294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216456</v>
+        <v>121216472</v>
       </c>
       <c r="B21" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,38 +2742,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511887</v>
+        <v>511926</v>
       </c>
       <c r="R21" t="n">
-        <v>6734253</v>
+        <v>6734295</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,10 +2841,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216486</v>
+        <v>121216462</v>
       </c>
       <c r="B22" t="n">
-        <v>100347</v>
+        <v>90995</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,25 +2853,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2854,10 +2881,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511930</v>
+        <v>511910</v>
       </c>
       <c r="R22" t="n">
-        <v>6734223</v>
+        <v>6734222</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2916,10 +2943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216489</v>
+        <v>121216454</v>
       </c>
       <c r="B23" t="n">
-        <v>100347</v>
+        <v>90709</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,25 +2955,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2956,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511874</v>
+        <v>511885</v>
       </c>
       <c r="R23" t="n">
-        <v>6734258</v>
+        <v>6734256</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,10 +3045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216472</v>
+        <v>121216460</v>
       </c>
       <c r="B24" t="n">
-        <v>98081</v>
+        <v>91149</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3034,43 +3061,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511926</v>
+        <v>511913</v>
       </c>
       <c r="R24" t="n">
-        <v>6734295</v>
+        <v>6734224</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,10 +3147,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216464</v>
+        <v>121216479</v>
       </c>
       <c r="B25" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3164,7 +3182,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3178,10 +3196,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511871</v>
+        <v>511944</v>
       </c>
       <c r="R25" t="n">
-        <v>6734288</v>
+        <v>6734302</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,10 +3258,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216488</v>
+        <v>121216461</v>
       </c>
       <c r="B26" t="n">
-        <v>100347</v>
+        <v>91149</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3252,25 +3270,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3280,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511890</v>
+        <v>511887</v>
       </c>
       <c r="R26" t="n">
-        <v>6734232</v>
+        <v>6734253</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3342,10 +3360,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216480</v>
+        <v>121216487</v>
       </c>
       <c r="B27" t="n">
-        <v>98081</v>
+        <v>100360</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3354,47 +3372,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511859</v>
+        <v>511896</v>
       </c>
       <c r="R27" t="n">
-        <v>6734287</v>
+        <v>6734236</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3453,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216462</v>
+        <v>121216467</v>
       </c>
       <c r="B28" t="n">
-        <v>90983</v>
+        <v>98094</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3465,38 +3474,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511910</v>
+        <v>511936</v>
       </c>
       <c r="R28" t="n">
-        <v>6734222</v>
+        <v>6734297</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3555,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216471</v>
+        <v>121216464</v>
       </c>
       <c r="B29" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3590,7 +3608,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3604,10 +3622,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511918</v>
+        <v>511871</v>
       </c>
       <c r="R29" t="n">
-        <v>6734292</v>
+        <v>6734288</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3666,10 +3684,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216482</v>
+        <v>121216486</v>
       </c>
       <c r="B30" t="n">
-        <v>98081</v>
+        <v>100360</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3678,47 +3696,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511946</v>
+        <v>511930</v>
       </c>
       <c r="R30" t="n">
-        <v>6734303</v>
+        <v>6734223</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3777,10 +3786,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216469</v>
+        <v>121216468</v>
       </c>
       <c r="B31" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3826,10 +3835,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511918</v>
+        <v>511953</v>
       </c>
       <c r="R31" t="n">
-        <v>6734258</v>
+        <v>6734306</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,10 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216474</v>
+        <v>121216488</v>
       </c>
       <c r="B32" t="n">
-        <v>98081</v>
+        <v>100360</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3900,47 +3909,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511908</v>
+        <v>511890</v>
       </c>
       <c r="R32" t="n">
-        <v>6734282</v>
+        <v>6734232</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,10 +3999,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216477</v>
+        <v>121216483</v>
       </c>
       <c r="B33" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511874</v>
+        <v>511919</v>
       </c>
       <c r="R33" t="n">
-        <v>6734290</v>
+        <v>6734255</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121216463</v>
       </c>
       <c r="B2" t="n">
-        <v>90995</v>
+        <v>90996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216476</v>
+        <v>121216471</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511926</v>
+        <v>511918</v>
       </c>
       <c r="R3" t="n">
-        <v>6734268</v>
+        <v>6734292</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216456</v>
+        <v>121216486</v>
       </c>
       <c r="B4" t="n">
-        <v>90709</v>
+        <v>100361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511887</v>
+        <v>511930</v>
       </c>
       <c r="R4" t="n">
-        <v>6734253</v>
+        <v>6734223</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216485</v>
+        <v>121216488</v>
       </c>
       <c r="B5" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511856</v>
+        <v>511890</v>
       </c>
       <c r="R5" t="n">
-        <v>6734258</v>
+        <v>6734232</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216469</v>
+        <v>121216490</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>100361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,47 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511918</v>
+        <v>511875</v>
       </c>
       <c r="R6" t="n">
-        <v>6734258</v>
+        <v>6734249</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216489</v>
+        <v>121216480</v>
       </c>
       <c r="B7" t="n">
-        <v>100360</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,38 +1206,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511874</v>
+        <v>511859</v>
       </c>
       <c r="R7" t="n">
-        <v>6734258</v>
+        <v>6734287</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216471</v>
+        <v>121216455</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>90710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,47 +1317,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511918</v>
+        <v>511912</v>
       </c>
       <c r="R8" t="n">
-        <v>6734292</v>
+        <v>6734222</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216477</v>
+        <v>121216465</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,7 +1442,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1465,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511874</v>
+        <v>511882</v>
       </c>
       <c r="R9" t="n">
-        <v>6734290</v>
+        <v>6734284</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216480</v>
+        <v>121216468</v>
       </c>
       <c r="B10" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,7 +1553,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1576,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511859</v>
+        <v>511953</v>
       </c>
       <c r="R10" t="n">
-        <v>6734287</v>
+        <v>6734306</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216474</v>
+        <v>121216460</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>91150</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,43 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511908</v>
+        <v>511913</v>
       </c>
       <c r="R11" t="n">
-        <v>6734282</v>
+        <v>6734224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216475</v>
+        <v>121216467</v>
       </c>
       <c r="B12" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,7 +1766,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1798,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511912</v>
+        <v>511936</v>
       </c>
       <c r="R12" t="n">
-        <v>6734269</v>
+        <v>6734297</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216490</v>
+        <v>121216464</v>
       </c>
       <c r="B13" t="n">
-        <v>100360</v>
+        <v>98095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,38 +1854,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511875</v>
+        <v>511871</v>
       </c>
       <c r="R13" t="n">
-        <v>6734249</v>
+        <v>6734288</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216466</v>
+        <v>121216472</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,7 +1988,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2011,7 +2002,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511896</v>
+        <v>511926</v>
       </c>
       <c r="R14" t="n">
         <v>6734295</v>
@@ -2073,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216465</v>
+        <v>121216466</v>
       </c>
       <c r="B15" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2122,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511882</v>
+        <v>511896</v>
       </c>
       <c r="R15" t="n">
-        <v>6734284</v>
+        <v>6734295</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216482</v>
+        <v>121216477</v>
       </c>
       <c r="B16" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2219,7 +2210,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2233,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511946</v>
+        <v>511874</v>
       </c>
       <c r="R16" t="n">
-        <v>6734303</v>
+        <v>6734290</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216478</v>
+        <v>121216476</v>
       </c>
       <c r="B17" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2330,7 +2321,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2344,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511932</v>
+        <v>511926</v>
       </c>
       <c r="R17" t="n">
-        <v>6734295</v>
+        <v>6734268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216455</v>
+        <v>121216456</v>
       </c>
       <c r="B18" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2446,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511912</v>
+        <v>511887</v>
       </c>
       <c r="R18" t="n">
-        <v>6734222</v>
+        <v>6734253</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,10 +2499,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216473</v>
+        <v>121216475</v>
       </c>
       <c r="B19" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2557,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511888</v>
+        <v>511912</v>
       </c>
       <c r="R19" t="n">
-        <v>6734296</v>
+        <v>6734269</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216481</v>
+        <v>121216473</v>
       </c>
       <c r="B20" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2654,7 +2645,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2668,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511892</v>
+        <v>511888</v>
       </c>
       <c r="R20" t="n">
-        <v>6734294</v>
+        <v>6734296</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,10 +2721,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216472</v>
+        <v>121216485</v>
       </c>
       <c r="B21" t="n">
-        <v>98094</v>
+        <v>100361</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2742,47 +2733,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511926</v>
+        <v>511856</v>
       </c>
       <c r="R21" t="n">
-        <v>6734295</v>
+        <v>6734258</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2841,10 +2823,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216462</v>
+        <v>121216478</v>
       </c>
       <c r="B22" t="n">
-        <v>90995</v>
+        <v>98095</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2853,38 +2835,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511910</v>
+        <v>511932</v>
       </c>
       <c r="R22" t="n">
-        <v>6734222</v>
+        <v>6734295</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2943,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216454</v>
+        <v>121216489</v>
       </c>
       <c r="B23" t="n">
-        <v>90709</v>
+        <v>100361</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2955,25 +2946,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511885</v>
+        <v>511874</v>
       </c>
       <c r="R23" t="n">
-        <v>6734256</v>
+        <v>6734258</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,10 +3036,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216460</v>
+        <v>121216482</v>
       </c>
       <c r="B24" t="n">
-        <v>91149</v>
+        <v>98095</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3061,34 +3052,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511913</v>
+        <v>511946</v>
       </c>
       <c r="R24" t="n">
-        <v>6734224</v>
+        <v>6734303</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216479</v>
+        <v>121216454</v>
       </c>
       <c r="B25" t="n">
-        <v>98094</v>
+        <v>90710</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3159,47 +3159,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511944</v>
+        <v>511885</v>
       </c>
       <c r="R25" t="n">
-        <v>6734302</v>
+        <v>6734256</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,10 +3249,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216461</v>
+        <v>121216462</v>
       </c>
       <c r="B26" t="n">
-        <v>91149</v>
+        <v>90996</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3270,25 +3261,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3298,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511887</v>
+        <v>511910</v>
       </c>
       <c r="R26" t="n">
-        <v>6734253</v>
+        <v>6734222</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,10 +3351,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216487</v>
+        <v>121216469</v>
       </c>
       <c r="B27" t="n">
-        <v>100360</v>
+        <v>98095</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3372,38 +3363,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511896</v>
+        <v>511918</v>
       </c>
       <c r="R27" t="n">
-        <v>6734236</v>
+        <v>6734258</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216467</v>
+        <v>121216461</v>
       </c>
       <c r="B28" t="n">
-        <v>98094</v>
+        <v>91150</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3478,43 +3478,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511936</v>
+        <v>511887</v>
       </c>
       <c r="R28" t="n">
-        <v>6734297</v>
+        <v>6734253</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216464</v>
+        <v>121216487</v>
       </c>
       <c r="B29" t="n">
-        <v>98094</v>
+        <v>100361</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3585,47 +3576,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511871</v>
+        <v>511896</v>
       </c>
       <c r="R29" t="n">
-        <v>6734288</v>
+        <v>6734236</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216486</v>
+        <v>121216479</v>
       </c>
       <c r="B30" t="n">
-        <v>100360</v>
+        <v>98095</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3696,38 +3678,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511930</v>
+        <v>511944</v>
       </c>
       <c r="R30" t="n">
-        <v>6734223</v>
+        <v>6734302</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,10 +3777,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216468</v>
+        <v>121216481</v>
       </c>
       <c r="B31" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3821,7 +3812,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3835,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511953</v>
+        <v>511892</v>
       </c>
       <c r="R31" t="n">
-        <v>6734306</v>
+        <v>6734294</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3897,10 +3888,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216488</v>
+        <v>121216474</v>
       </c>
       <c r="B32" t="n">
-        <v>100360</v>
+        <v>98095</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3909,38 +3900,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511890</v>
+        <v>511908</v>
       </c>
       <c r="R32" t="n">
-        <v>6734232</v>
+        <v>6734282</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4002,7 +4002,7 @@
         <v>121216483</v>
       </c>
       <c r="B33" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216463</v>
+        <v>121216474</v>
       </c>
       <c r="B2" t="n">
-        <v>90996</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511882</v>
+        <v>511908</v>
       </c>
       <c r="R2" t="n">
-        <v>6734252</v>
+        <v>6734282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216471</v>
+        <v>121216466</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511918</v>
+        <v>511896</v>
       </c>
       <c r="R3" t="n">
-        <v>6734292</v>
+        <v>6734295</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,7 +900,7 @@
         <v>121216486</v>
       </c>
       <c r="B4" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -990,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216488</v>
+        <v>121216464</v>
       </c>
       <c r="B5" t="n">
-        <v>100361</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +1011,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511890</v>
+        <v>511871</v>
       </c>
       <c r="R5" t="n">
-        <v>6734232</v>
+        <v>6734288</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216490</v>
+        <v>121216487</v>
       </c>
       <c r="B6" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511875</v>
+        <v>511896</v>
       </c>
       <c r="R6" t="n">
-        <v>6734249</v>
+        <v>6734236</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216480</v>
+        <v>121216478</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,7 +1247,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1243,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511859</v>
+        <v>511932</v>
       </c>
       <c r="R7" t="n">
-        <v>6734287</v>
+        <v>6734295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216455</v>
+        <v>121216456</v>
       </c>
       <c r="B8" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511912</v>
+        <v>511887</v>
       </c>
       <c r="R8" t="n">
-        <v>6734222</v>
+        <v>6734253</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216465</v>
+        <v>121216477</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1456,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511882</v>
+        <v>511874</v>
       </c>
       <c r="R9" t="n">
-        <v>6734284</v>
+        <v>6734290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216468</v>
+        <v>121216473</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,7 +1571,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1567,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511953</v>
+        <v>511888</v>
       </c>
       <c r="R10" t="n">
-        <v>6734306</v>
+        <v>6734296</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216460</v>
+        <v>121216468</v>
       </c>
       <c r="B11" t="n">
-        <v>91150</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1663,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511913</v>
+        <v>511953</v>
       </c>
       <c r="R11" t="n">
-        <v>6734224</v>
+        <v>6734306</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216467</v>
+        <v>121216483</v>
       </c>
       <c r="B12" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,7 +1793,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1780,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511936</v>
+        <v>511919</v>
       </c>
       <c r="R12" t="n">
-        <v>6734297</v>
+        <v>6734255</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216464</v>
+        <v>121216490</v>
       </c>
       <c r="B13" t="n">
-        <v>98095</v>
+        <v>100364</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,47 +1881,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511871</v>
+        <v>511875</v>
       </c>
       <c r="R13" t="n">
-        <v>6734288</v>
+        <v>6734249</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216472</v>
+        <v>121216485</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>100364</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,47 +1983,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511926</v>
+        <v>511856</v>
       </c>
       <c r="R14" t="n">
-        <v>6734295</v>
+        <v>6734258</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216466</v>
+        <v>121216482</v>
       </c>
       <c r="B15" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,7 +2108,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2113,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511896</v>
+        <v>511946</v>
       </c>
       <c r="R15" t="n">
-        <v>6734295</v>
+        <v>6734303</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216477</v>
+        <v>121216476</v>
       </c>
       <c r="B16" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,7 +2219,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2224,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511874</v>
+        <v>511926</v>
       </c>
       <c r="R16" t="n">
-        <v>6734290</v>
+        <v>6734268</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216476</v>
+        <v>121216471</v>
       </c>
       <c r="B17" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,7 +2330,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2335,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511926</v>
+        <v>511918</v>
       </c>
       <c r="R17" t="n">
-        <v>6734268</v>
+        <v>6734292</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216456</v>
+        <v>121216454</v>
       </c>
       <c r="B18" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2437,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511887</v>
+        <v>511885</v>
       </c>
       <c r="R18" t="n">
-        <v>6734253</v>
+        <v>6734256</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,10 +2508,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216475</v>
+        <v>121216469</v>
       </c>
       <c r="B19" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,7 +2543,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2548,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511912</v>
+        <v>511918</v>
       </c>
       <c r="R19" t="n">
-        <v>6734269</v>
+        <v>6734258</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2610,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216473</v>
+        <v>121216481</v>
       </c>
       <c r="B20" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2645,7 +2654,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2659,10 +2668,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511888</v>
+        <v>511892</v>
       </c>
       <c r="R20" t="n">
-        <v>6734296</v>
+        <v>6734294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216485</v>
+        <v>121216480</v>
       </c>
       <c r="B21" t="n">
-        <v>100361</v>
+        <v>98098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,38 +2742,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511856</v>
+        <v>511859</v>
       </c>
       <c r="R21" t="n">
-        <v>6734258</v>
+        <v>6734287</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,10 +2841,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216478</v>
+        <v>121216475</v>
       </c>
       <c r="B22" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2858,7 +2876,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2872,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511932</v>
+        <v>511912</v>
       </c>
       <c r="R22" t="n">
-        <v>6734295</v>
+        <v>6734269</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216489</v>
+        <v>121216488</v>
       </c>
       <c r="B23" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2974,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511874</v>
+        <v>511890</v>
       </c>
       <c r="R23" t="n">
-        <v>6734258</v>
+        <v>6734232</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,10 +3054,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216482</v>
+        <v>121216460</v>
       </c>
       <c r="B24" t="n">
-        <v>98095</v>
+        <v>91153</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3052,43 +3070,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511946</v>
+        <v>511913</v>
       </c>
       <c r="R24" t="n">
-        <v>6734303</v>
+        <v>6734224</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216454</v>
+        <v>121216462</v>
       </c>
       <c r="B25" t="n">
-        <v>90710</v>
+        <v>90999</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3163,21 +3172,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3187,10 +3196,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511885</v>
+        <v>511910</v>
       </c>
       <c r="R25" t="n">
-        <v>6734256</v>
+        <v>6734222</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,10 +3258,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216462</v>
+        <v>121216467</v>
       </c>
       <c r="B26" t="n">
-        <v>90996</v>
+        <v>98098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3261,38 +3270,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511910</v>
+        <v>511936</v>
       </c>
       <c r="R26" t="n">
-        <v>6734222</v>
+        <v>6734297</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3351,10 +3369,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216469</v>
+        <v>121216465</v>
       </c>
       <c r="B27" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3400,10 +3418,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511918</v>
+        <v>511882</v>
       </c>
       <c r="R27" t="n">
-        <v>6734258</v>
+        <v>6734284</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3465,7 +3483,7 @@
         <v>121216461</v>
       </c>
       <c r="B28" t="n">
-        <v>91150</v>
+        <v>91153</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3564,10 +3582,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216487</v>
+        <v>121216489</v>
       </c>
       <c r="B29" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3604,10 +3622,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511896</v>
+        <v>511874</v>
       </c>
       <c r="R29" t="n">
-        <v>6734236</v>
+        <v>6734258</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3666,10 +3684,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216479</v>
+        <v>121216455</v>
       </c>
       <c r="B30" t="n">
-        <v>98095</v>
+        <v>90713</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3678,47 +3696,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511944</v>
+        <v>511912</v>
       </c>
       <c r="R30" t="n">
-        <v>6734302</v>
+        <v>6734222</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3777,10 +3786,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216481</v>
+        <v>121216479</v>
       </c>
       <c r="B31" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3812,7 +3821,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3826,10 +3835,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511892</v>
+        <v>511944</v>
       </c>
       <c r="R31" t="n">
-        <v>6734294</v>
+        <v>6734302</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,10 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216474</v>
+        <v>121216463</v>
       </c>
       <c r="B32" t="n">
-        <v>98095</v>
+        <v>90999</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3900,47 +3909,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511908</v>
+        <v>511882</v>
       </c>
       <c r="R32" t="n">
-        <v>6734282</v>
+        <v>6734252</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,10 +3999,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216483</v>
+        <v>121216472</v>
       </c>
       <c r="B33" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511919</v>
+        <v>511926</v>
       </c>
       <c r="R33" t="n">
-        <v>6734255</v>
+        <v>6734295</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216474</v>
+        <v>121216488</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>100364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511908</v>
+        <v>511890</v>
       </c>
       <c r="R2" t="n">
-        <v>6734282</v>
+        <v>6734232</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216466</v>
+        <v>121216455</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511896</v>
+        <v>511912</v>
       </c>
       <c r="R3" t="n">
-        <v>6734295</v>
+        <v>6734222</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216486</v>
+        <v>121216465</v>
       </c>
       <c r="B4" t="n">
-        <v>100364</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +891,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511930</v>
+        <v>511882</v>
       </c>
       <c r="R4" t="n">
-        <v>6734223</v>
+        <v>6734284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216464</v>
+        <v>121216476</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1034,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511871</v>
+        <v>511926</v>
       </c>
       <c r="R5" t="n">
-        <v>6734288</v>
+        <v>6734268</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216487</v>
+        <v>121216469</v>
       </c>
       <c r="B6" t="n">
-        <v>100364</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,38 +1113,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511896</v>
+        <v>511918</v>
       </c>
       <c r="R6" t="n">
-        <v>6734236</v>
+        <v>6734258</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216478</v>
+        <v>121216477</v>
       </c>
       <c r="B7" t="n">
         <v>98098</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511932</v>
+        <v>511874</v>
       </c>
       <c r="R7" t="n">
-        <v>6734295</v>
+        <v>6734290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216456</v>
+        <v>121216486</v>
       </c>
       <c r="B8" t="n">
-        <v>90713</v>
+        <v>100364</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,25 +1335,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511887</v>
+        <v>511930</v>
       </c>
       <c r="R8" t="n">
-        <v>6734253</v>
+        <v>6734223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216477</v>
+        <v>121216464</v>
       </c>
       <c r="B9" t="n">
         <v>98098</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511874</v>
+        <v>511871</v>
       </c>
       <c r="R9" t="n">
-        <v>6734290</v>
+        <v>6734288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216473</v>
+        <v>121216485</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>100364</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,47 +1548,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511888</v>
+        <v>511856</v>
       </c>
       <c r="R10" t="n">
-        <v>6734296</v>
+        <v>6734258</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216468</v>
+        <v>121216462</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>90999</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,47 +1650,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511953</v>
+        <v>511910</v>
       </c>
       <c r="R11" t="n">
-        <v>6734306</v>
+        <v>6734222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216483</v>
+        <v>121216471</v>
       </c>
       <c r="B12" t="n">
         <v>98098</v>
@@ -1793,7 +1775,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1807,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511919</v>
+        <v>511918</v>
       </c>
       <c r="R12" t="n">
-        <v>6734255</v>
+        <v>6734292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216490</v>
+        <v>121216473</v>
       </c>
       <c r="B13" t="n">
-        <v>100364</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,38 +1863,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511875</v>
+        <v>511888</v>
       </c>
       <c r="R13" t="n">
-        <v>6734249</v>
+        <v>6734296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216485</v>
+        <v>121216481</v>
       </c>
       <c r="B14" t="n">
-        <v>100364</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,38 +1974,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511856</v>
+        <v>511892</v>
       </c>
       <c r="R14" t="n">
-        <v>6734258</v>
+        <v>6734294</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216482</v>
+        <v>121216489</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>100364</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,47 +2085,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511946</v>
+        <v>511874</v>
       </c>
       <c r="R15" t="n">
-        <v>6734303</v>
+        <v>6734258</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216476</v>
+        <v>121216474</v>
       </c>
       <c r="B16" t="n">
         <v>98098</v>
@@ -2219,7 +2210,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2233,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511926</v>
+        <v>511908</v>
       </c>
       <c r="R16" t="n">
-        <v>6734268</v>
+        <v>6734282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216471</v>
+        <v>121216460</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>91153</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,43 +2302,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511918</v>
+        <v>511913</v>
       </c>
       <c r="R17" t="n">
-        <v>6734292</v>
+        <v>6734224</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,10 +2388,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216454</v>
+        <v>121216482</v>
       </c>
       <c r="B18" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,38 +2400,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511885</v>
+        <v>511946</v>
       </c>
       <c r="R18" t="n">
-        <v>6734256</v>
+        <v>6734303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,10 +2499,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216469</v>
+        <v>121216487</v>
       </c>
       <c r="B19" t="n">
-        <v>98098</v>
+        <v>100364</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,47 +2511,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511918</v>
+        <v>511896</v>
       </c>
       <c r="R19" t="n">
-        <v>6734258</v>
+        <v>6734236</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216481</v>
+        <v>121216490</v>
       </c>
       <c r="B20" t="n">
-        <v>98098</v>
+        <v>100364</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,47 +2613,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511892</v>
+        <v>511875</v>
       </c>
       <c r="R20" t="n">
-        <v>6734294</v>
+        <v>6734249</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216480</v>
+        <v>121216483</v>
       </c>
       <c r="B21" t="n">
         <v>98098</v>
@@ -2779,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511859</v>
+        <v>511919</v>
       </c>
       <c r="R21" t="n">
-        <v>6734287</v>
+        <v>6734255</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2841,7 +2814,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216475</v>
+        <v>121216467</v>
       </c>
       <c r="B22" t="n">
         <v>98098</v>
@@ -2876,7 +2849,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2890,10 +2863,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511912</v>
+        <v>511936</v>
       </c>
       <c r="R22" t="n">
-        <v>6734269</v>
+        <v>6734297</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,10 +2925,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216488</v>
+        <v>121216456</v>
       </c>
       <c r="B23" t="n">
-        <v>100364</v>
+        <v>90713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2964,25 +2937,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2992,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511890</v>
+        <v>511887</v>
       </c>
       <c r="R23" t="n">
-        <v>6734232</v>
+        <v>6734253</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3054,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216460</v>
+        <v>121216472</v>
       </c>
       <c r="B24" t="n">
-        <v>91153</v>
+        <v>98098</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3070,34 +3043,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511913</v>
+        <v>511926</v>
       </c>
       <c r="R24" t="n">
-        <v>6734224</v>
+        <v>6734295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3156,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216462</v>
+        <v>121216480</v>
       </c>
       <c r="B25" t="n">
-        <v>90999</v>
+        <v>98098</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3168,38 +3150,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511910</v>
+        <v>511859</v>
       </c>
       <c r="R25" t="n">
-        <v>6734222</v>
+        <v>6734287</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,7 +3249,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216467</v>
+        <v>121216478</v>
       </c>
       <c r="B26" t="n">
         <v>98098</v>
@@ -3293,7 +3284,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3307,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511936</v>
+        <v>511932</v>
       </c>
       <c r="R26" t="n">
-        <v>6734297</v>
+        <v>6734295</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,10 +3360,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216465</v>
+        <v>121216461</v>
       </c>
       <c r="B27" t="n">
-        <v>98098</v>
+        <v>91153</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3385,43 +3376,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511882</v>
+        <v>511887</v>
       </c>
       <c r="R27" t="n">
-        <v>6734284</v>
+        <v>6734253</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3480,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216461</v>
+        <v>121216475</v>
       </c>
       <c r="B28" t="n">
-        <v>91153</v>
+        <v>98098</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3496,34 +3478,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511887</v>
+        <v>511912</v>
       </c>
       <c r="R28" t="n">
-        <v>6734253</v>
+        <v>6734269</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3582,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216489</v>
+        <v>121216463</v>
       </c>
       <c r="B29" t="n">
-        <v>100364</v>
+        <v>90999</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3594,25 +3585,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3622,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511874</v>
+        <v>511882</v>
       </c>
       <c r="R29" t="n">
-        <v>6734258</v>
+        <v>6734252</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3675,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216455</v>
+        <v>121216454</v>
       </c>
       <c r="B30" t="n">
         <v>90713</v>
@@ -3724,10 +3715,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511912</v>
+        <v>511885</v>
       </c>
       <c r="R30" t="n">
-        <v>6734222</v>
+        <v>6734256</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,10 +3888,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216463</v>
+        <v>121216466</v>
       </c>
       <c r="B32" t="n">
-        <v>90999</v>
+        <v>98098</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3909,38 +3900,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511882</v>
+        <v>511896</v>
       </c>
       <c r="R32" t="n">
-        <v>6734252</v>
+        <v>6734295</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216472</v>
+        <v>121216468</v>
       </c>
       <c r="B33" t="n">
         <v>98098</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511926</v>
+        <v>511953</v>
       </c>
       <c r="R33" t="n">
-        <v>6734295</v>
+        <v>6734306</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216455</v>
+        <v>121216465</v>
       </c>
       <c r="B3" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511912</v>
+        <v>511882</v>
       </c>
       <c r="R3" t="n">
-        <v>6734222</v>
+        <v>6734284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216465</v>
+        <v>121216476</v>
       </c>
       <c r="B4" t="n">
         <v>98098</v>
@@ -914,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -928,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511882</v>
+        <v>511926</v>
       </c>
       <c r="R4" t="n">
-        <v>6734284</v>
+        <v>6734268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216476</v>
+        <v>121216455</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,47 +1011,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511926</v>
+        <v>511912</v>
       </c>
       <c r="R5" t="n">
-        <v>6734268</v>
+        <v>6734222</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216454</v>
+        <v>121216479</v>
       </c>
       <c r="B30" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3687,38 +3687,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511885</v>
+        <v>511944</v>
       </c>
       <c r="R30" t="n">
-        <v>6734256</v>
+        <v>6734302</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3777,10 +3786,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216479</v>
+        <v>121216454</v>
       </c>
       <c r="B31" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3789,47 +3798,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511944</v>
+        <v>511885</v>
       </c>
       <c r="R31" t="n">
-        <v>6734302</v>
+        <v>6734256</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216488</v>
+        <v>121216465</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511890</v>
+        <v>511882</v>
       </c>
       <c r="R2" t="n">
-        <v>6734232</v>
+        <v>6734284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216465</v>
+        <v>121216476</v>
       </c>
       <c r="B3" t="n">
         <v>98098</v>
@@ -812,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511882</v>
+        <v>511926</v>
       </c>
       <c r="R3" t="n">
-        <v>6734284</v>
+        <v>6734268</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216476</v>
+        <v>121216488</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>100364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,47 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511926</v>
+        <v>511890</v>
       </c>
       <c r="R4" t="n">
-        <v>6734268</v>
+        <v>6734232</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216479</v>
+        <v>121216454</v>
       </c>
       <c r="B30" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3687,47 +3687,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511944</v>
+        <v>511885</v>
       </c>
       <c r="R30" t="n">
-        <v>6734302</v>
+        <v>6734256</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,10 +3777,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216454</v>
+        <v>121216479</v>
       </c>
       <c r="B31" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3798,38 +3789,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511885</v>
+        <v>511944</v>
       </c>
       <c r="R31" t="n">
-        <v>6734256</v>
+        <v>6734302</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216465</v>
+        <v>121216455</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511882</v>
+        <v>511912</v>
       </c>
       <c r="R2" t="n">
-        <v>6734284</v>
+        <v>6734222</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216476</v>
+        <v>121216473</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511926</v>
+        <v>511888</v>
       </c>
       <c r="R3" t="n">
-        <v>6734268</v>
+        <v>6734296</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216488</v>
+        <v>121216465</v>
       </c>
       <c r="B4" t="n">
-        <v>100364</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +900,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511890</v>
+        <v>511882</v>
       </c>
       <c r="R4" t="n">
-        <v>6734232</v>
+        <v>6734284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216455</v>
+        <v>121216490</v>
       </c>
       <c r="B5" t="n">
-        <v>90713</v>
+        <v>100370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511912</v>
+        <v>511875</v>
       </c>
       <c r="R5" t="n">
-        <v>6734222</v>
+        <v>6734249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216469</v>
+        <v>121216454</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,47 +1113,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511918</v>
+        <v>511885</v>
       </c>
       <c r="R6" t="n">
-        <v>6734258</v>
+        <v>6734256</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216477</v>
+        <v>121216468</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,7 +1238,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1261,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511874</v>
+        <v>511953</v>
       </c>
       <c r="R7" t="n">
-        <v>6734290</v>
+        <v>6734306</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216486</v>
+        <v>121216477</v>
       </c>
       <c r="B8" t="n">
-        <v>100364</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,38 +1326,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511930</v>
+        <v>511874</v>
       </c>
       <c r="R8" t="n">
-        <v>6734223</v>
+        <v>6734290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216464</v>
+        <v>121216475</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511871</v>
+        <v>511912</v>
       </c>
       <c r="R9" t="n">
-        <v>6734288</v>
+        <v>6734269</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216485</v>
+        <v>121216466</v>
       </c>
       <c r="B10" t="n">
-        <v>100364</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,38 +1548,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511856</v>
+        <v>511896</v>
       </c>
       <c r="R10" t="n">
-        <v>6734258</v>
+        <v>6734295</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216462</v>
+        <v>121216488</v>
       </c>
       <c r="B11" t="n">
-        <v>90999</v>
+        <v>100370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,25 +1659,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511910</v>
+        <v>511890</v>
       </c>
       <c r="R11" t="n">
-        <v>6734222</v>
+        <v>6734232</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216471</v>
+        <v>121216460</v>
       </c>
       <c r="B12" t="n">
-        <v>98098</v>
+        <v>91159</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,43 +1765,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511918</v>
+        <v>511913</v>
       </c>
       <c r="R12" t="n">
-        <v>6734292</v>
+        <v>6734224</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216473</v>
+        <v>121216481</v>
       </c>
       <c r="B13" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511888</v>
+        <v>511892</v>
       </c>
       <c r="R13" t="n">
-        <v>6734296</v>
+        <v>6734294</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216481</v>
+        <v>121216471</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511892</v>
+        <v>511918</v>
       </c>
       <c r="R14" t="n">
-        <v>6734294</v>
+        <v>6734292</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216489</v>
+        <v>121216487</v>
       </c>
       <c r="B15" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511874</v>
+        <v>511896</v>
       </c>
       <c r="R15" t="n">
-        <v>6734258</v>
+        <v>6734236</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216474</v>
+        <v>121216469</v>
       </c>
       <c r="B16" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511908</v>
+        <v>511918</v>
       </c>
       <c r="R16" t="n">
-        <v>6734282</v>
+        <v>6734258</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216460</v>
+        <v>121216474</v>
       </c>
       <c r="B17" t="n">
-        <v>91153</v>
+        <v>98104</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2302,34 +2302,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511913</v>
+        <v>511908</v>
       </c>
       <c r="R17" t="n">
-        <v>6734224</v>
+        <v>6734282</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216482</v>
+        <v>121216480</v>
       </c>
       <c r="B18" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2437,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511946</v>
+        <v>511859</v>
       </c>
       <c r="R18" t="n">
-        <v>6734303</v>
+        <v>6734287</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,10 +2508,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216487</v>
+        <v>121216482</v>
       </c>
       <c r="B19" t="n">
-        <v>100364</v>
+        <v>98104</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2511,38 +2520,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511896</v>
+        <v>511946</v>
       </c>
       <c r="R19" t="n">
-        <v>6734236</v>
+        <v>6734303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216490</v>
+        <v>121216464</v>
       </c>
       <c r="B20" t="n">
-        <v>100364</v>
+        <v>98104</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2613,38 +2631,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511875</v>
+        <v>511871</v>
       </c>
       <c r="R20" t="n">
-        <v>6734249</v>
+        <v>6734288</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216483</v>
+        <v>121216462</v>
       </c>
       <c r="B21" t="n">
-        <v>98098</v>
+        <v>91005</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,47 +2742,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511919</v>
+        <v>511910</v>
       </c>
       <c r="R21" t="n">
-        <v>6734255</v>
+        <v>6734222</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,10 +2832,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216467</v>
+        <v>121216463</v>
       </c>
       <c r="B22" t="n">
-        <v>98098</v>
+        <v>91005</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,47 +2844,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511936</v>
+        <v>511882</v>
       </c>
       <c r="R22" t="n">
-        <v>6734297</v>
+        <v>6734252</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216456</v>
+        <v>121216485</v>
       </c>
       <c r="B23" t="n">
-        <v>90713</v>
+        <v>100370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2937,25 +2946,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2965,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511887</v>
+        <v>511856</v>
       </c>
       <c r="R23" t="n">
-        <v>6734253</v>
+        <v>6734258</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,7 +3039,7 @@
         <v>121216472</v>
       </c>
       <c r="B24" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3138,10 +3147,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216480</v>
+        <v>121216483</v>
       </c>
       <c r="B25" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3187,10 +3196,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511859</v>
+        <v>511919</v>
       </c>
       <c r="R25" t="n">
-        <v>6734287</v>
+        <v>6734255</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,10 +3258,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216478</v>
+        <v>121216456</v>
       </c>
       <c r="B26" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3261,47 +3270,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511932</v>
+        <v>511887</v>
       </c>
       <c r="R26" t="n">
-        <v>6734295</v>
+        <v>6734253</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,10 +3360,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216461</v>
+        <v>121216489</v>
       </c>
       <c r="B27" t="n">
-        <v>91153</v>
+        <v>100370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3372,25 +3372,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511887</v>
+        <v>511874</v>
       </c>
       <c r="R27" t="n">
-        <v>6734253</v>
+        <v>6734258</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216475</v>
+        <v>121216461</v>
       </c>
       <c r="B28" t="n">
-        <v>98098</v>
+        <v>91159</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3478,43 +3478,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511912</v>
+        <v>511887</v>
       </c>
       <c r="R28" t="n">
-        <v>6734269</v>
+        <v>6734253</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3573,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216463</v>
+        <v>121216467</v>
       </c>
       <c r="B29" t="n">
-        <v>90999</v>
+        <v>98104</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3585,38 +3576,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511882</v>
+        <v>511936</v>
       </c>
       <c r="R29" t="n">
-        <v>6734252</v>
+        <v>6734297</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216454</v>
+        <v>121216478</v>
       </c>
       <c r="B30" t="n">
-        <v>90713</v>
+        <v>98104</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3687,38 +3687,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511885</v>
+        <v>511932</v>
       </c>
       <c r="R30" t="n">
-        <v>6734256</v>
+        <v>6734295</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3780,7 +3789,7 @@
         <v>121216479</v>
       </c>
       <c r="B31" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3888,10 +3897,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216466</v>
+        <v>121216486</v>
       </c>
       <c r="B32" t="n">
-        <v>98098</v>
+        <v>100370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3900,47 +3909,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511896</v>
+        <v>511930</v>
       </c>
       <c r="R32" t="n">
-        <v>6734295</v>
+        <v>6734223</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,10 +3999,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216468</v>
+        <v>121216476</v>
       </c>
       <c r="B33" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511953</v>
+        <v>511926</v>
       </c>
       <c r="R33" t="n">
-        <v>6734306</v>
+        <v>6734268</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216487</v>
+        <v>121216469</v>
       </c>
       <c r="B15" t="n">
-        <v>100370</v>
+        <v>98104</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,38 +2085,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511896</v>
+        <v>511918</v>
       </c>
       <c r="R15" t="n">
-        <v>6734236</v>
+        <v>6734258</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2184,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216469</v>
+        <v>121216474</v>
       </c>
       <c r="B16" t="n">
         <v>98104</v>
@@ -2210,7 +2219,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2224,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511918</v>
+        <v>511908</v>
       </c>
       <c r="R16" t="n">
-        <v>6734258</v>
+        <v>6734282</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216474</v>
+        <v>121216487</v>
       </c>
       <c r="B17" t="n">
-        <v>98104</v>
+        <v>100370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,47 +2307,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511908</v>
+        <v>511896</v>
       </c>
       <c r="R17" t="n">
-        <v>6734282</v>
+        <v>6734236</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216472</v>
+        <v>121216489</v>
       </c>
       <c r="B24" t="n">
-        <v>98104</v>
+        <v>100370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3048,47 +3048,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511926</v>
+        <v>511874</v>
       </c>
       <c r="R24" t="n">
-        <v>6734295</v>
+        <v>6734258</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,7 +3138,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216483</v>
+        <v>121216472</v>
       </c>
       <c r="B25" t="n">
         <v>98104</v>
@@ -3182,7 +3173,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3196,10 +3187,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511919</v>
+        <v>511926</v>
       </c>
       <c r="R25" t="n">
-        <v>6734255</v>
+        <v>6734295</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,10 +3249,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216456</v>
+        <v>121216483</v>
       </c>
       <c r="B26" t="n">
-        <v>90719</v>
+        <v>98104</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3270,38 +3261,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511887</v>
+        <v>511919</v>
       </c>
       <c r="R26" t="n">
-        <v>6734253</v>
+        <v>6734255</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,10 +3360,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216489</v>
+        <v>121216456</v>
       </c>
       <c r="B27" t="n">
-        <v>100370</v>
+        <v>90719</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3372,25 +3372,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511874</v>
+        <v>511887</v>
       </c>
       <c r="R27" t="n">
-        <v>6734258</v>
+        <v>6734253</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216455</v>
+        <v>121216465</v>
       </c>
       <c r="B2" t="n">
-        <v>90719</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511912</v>
+        <v>511882</v>
       </c>
       <c r="R2" t="n">
-        <v>6734222</v>
+        <v>6734284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216473</v>
+        <v>121216489</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>100371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511888</v>
+        <v>511874</v>
       </c>
       <c r="R3" t="n">
-        <v>6734296</v>
+        <v>6734258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216465</v>
+        <v>121216455</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,47 +900,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511882</v>
+        <v>511912</v>
       </c>
       <c r="R4" t="n">
-        <v>6734284</v>
+        <v>6734222</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216490</v>
+        <v>121216488</v>
       </c>
       <c r="B5" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511875</v>
+        <v>511890</v>
       </c>
       <c r="R5" t="n">
-        <v>6734249</v>
+        <v>6734232</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216454</v>
+        <v>121216481</v>
       </c>
       <c r="B6" t="n">
-        <v>90719</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,38 +1104,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511885</v>
+        <v>511892</v>
       </c>
       <c r="R6" t="n">
-        <v>6734256</v>
+        <v>6734294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216468</v>
+        <v>121216483</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511953</v>
+        <v>511919</v>
       </c>
       <c r="R7" t="n">
-        <v>6734306</v>
+        <v>6734255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216477</v>
+        <v>121216486</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>100371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,47 +1326,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511874</v>
+        <v>511930</v>
       </c>
       <c r="R8" t="n">
-        <v>6734290</v>
+        <v>6734223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216475</v>
+        <v>121216461</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>91160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,43 +1432,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511912</v>
+        <v>511887</v>
       </c>
       <c r="R9" t="n">
-        <v>6734269</v>
+        <v>6734253</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216466</v>
+        <v>121216463</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>91006</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,47 +1530,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511896</v>
+        <v>511882</v>
       </c>
       <c r="R10" t="n">
-        <v>6734295</v>
+        <v>6734252</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216488</v>
+        <v>121216474</v>
       </c>
       <c r="B11" t="n">
-        <v>100370</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,38 +1632,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511890</v>
+        <v>511908</v>
       </c>
       <c r="R11" t="n">
-        <v>6734232</v>
+        <v>6734282</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216460</v>
+        <v>121216456</v>
       </c>
       <c r="B12" t="n">
-        <v>91159</v>
+        <v>90720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,25 +1743,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1789,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511913</v>
+        <v>511887</v>
       </c>
       <c r="R12" t="n">
-        <v>6734224</v>
+        <v>6734253</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216481</v>
+        <v>121216466</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,7 +1868,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1900,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511892</v>
+        <v>511896</v>
       </c>
       <c r="R13" t="n">
-        <v>6734294</v>
+        <v>6734295</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216471</v>
+        <v>121216487</v>
       </c>
       <c r="B14" t="n">
-        <v>98104</v>
+        <v>100371</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,47 +1956,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511918</v>
+        <v>511896</v>
       </c>
       <c r="R14" t="n">
-        <v>6734292</v>
+        <v>6734236</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216469</v>
+        <v>121216471</v>
       </c>
       <c r="B15" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2108,7 +2081,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2125,7 +2098,7 @@
         <v>511918</v>
       </c>
       <c r="R15" t="n">
-        <v>6734258</v>
+        <v>6734292</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2157,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216474</v>
+        <v>121216454</v>
       </c>
       <c r="B16" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2196,47 +2169,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511908</v>
+        <v>511885</v>
       </c>
       <c r="R16" t="n">
-        <v>6734282</v>
+        <v>6734256</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,10 +2259,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216487</v>
+        <v>121216477</v>
       </c>
       <c r="B17" t="n">
-        <v>100370</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,38 +2271,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511896</v>
+        <v>511874</v>
       </c>
       <c r="R17" t="n">
-        <v>6734236</v>
+        <v>6734290</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2370,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216480</v>
+        <v>121216476</v>
       </c>
       <c r="B18" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2432,7 +2405,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2446,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511859</v>
+        <v>511926</v>
       </c>
       <c r="R18" t="n">
-        <v>6734287</v>
+        <v>6734268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216482</v>
+        <v>121216460</v>
       </c>
       <c r="B19" t="n">
-        <v>98104</v>
+        <v>91160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2524,43 +2497,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511946</v>
+        <v>511913</v>
       </c>
       <c r="R19" t="n">
-        <v>6734303</v>
+        <v>6734224</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216464</v>
+        <v>121216482</v>
       </c>
       <c r="B20" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2654,7 +2618,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2668,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511871</v>
+        <v>511946</v>
       </c>
       <c r="R20" t="n">
-        <v>6734288</v>
+        <v>6734303</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216462</v>
+        <v>121216490</v>
       </c>
       <c r="B21" t="n">
-        <v>91005</v>
+        <v>100371</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2742,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2770,10 +2734,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511910</v>
+        <v>511875</v>
       </c>
       <c r="R21" t="n">
-        <v>6734222</v>
+        <v>6734249</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2832,10 +2796,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216463</v>
+        <v>121216464</v>
       </c>
       <c r="B22" t="n">
-        <v>91005</v>
+        <v>98105</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2844,38 +2808,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511882</v>
+        <v>511871</v>
       </c>
       <c r="R22" t="n">
-        <v>6734252</v>
+        <v>6734288</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216485</v>
+        <v>121216472</v>
       </c>
       <c r="B23" t="n">
-        <v>100370</v>
+        <v>98105</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2946,38 +2919,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511856</v>
+        <v>511926</v>
       </c>
       <c r="R23" t="n">
-        <v>6734258</v>
+        <v>6734295</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,10 +3018,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216489</v>
+        <v>121216485</v>
       </c>
       <c r="B24" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3076,7 +3058,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511874</v>
+        <v>511856</v>
       </c>
       <c r="R24" t="n">
         <v>6734258</v>
@@ -3138,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216472</v>
+        <v>121216462</v>
       </c>
       <c r="B25" t="n">
-        <v>98104</v>
+        <v>91006</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3150,47 +3132,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511926</v>
+        <v>511910</v>
       </c>
       <c r="R25" t="n">
-        <v>6734295</v>
+        <v>6734222</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,10 +3222,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216483</v>
+        <v>121216475</v>
       </c>
       <c r="B26" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3284,7 +3257,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3298,10 +3271,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511919</v>
+        <v>511912</v>
       </c>
       <c r="R26" t="n">
-        <v>6734255</v>
+        <v>6734269</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216456</v>
+        <v>121216467</v>
       </c>
       <c r="B27" t="n">
-        <v>90719</v>
+        <v>98105</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3372,38 +3345,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511887</v>
+        <v>511936</v>
       </c>
       <c r="R27" t="n">
-        <v>6734253</v>
+        <v>6734297</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,10 +3444,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216461</v>
+        <v>121216473</v>
       </c>
       <c r="B28" t="n">
-        <v>91159</v>
+        <v>98105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3478,34 +3460,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511887</v>
+        <v>511888</v>
       </c>
       <c r="R28" t="n">
-        <v>6734253</v>
+        <v>6734296</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216467</v>
+        <v>121216480</v>
       </c>
       <c r="B29" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3599,7 +3590,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3613,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511936</v>
+        <v>511859</v>
       </c>
       <c r="R29" t="n">
-        <v>6734297</v>
+        <v>6734287</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216478</v>
+        <v>121216479</v>
       </c>
       <c r="B30" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3724,10 +3715,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511932</v>
+        <v>511944</v>
       </c>
       <c r="R30" t="n">
-        <v>6734295</v>
+        <v>6734302</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,10 +3777,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216479</v>
+        <v>121216478</v>
       </c>
       <c r="B31" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3835,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511944</v>
+        <v>511932</v>
       </c>
       <c r="R31" t="n">
-        <v>6734302</v>
+        <v>6734295</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3897,10 +3888,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216486</v>
+        <v>121216469</v>
       </c>
       <c r="B32" t="n">
-        <v>100370</v>
+        <v>98105</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3909,38 +3900,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511930</v>
+        <v>511918</v>
       </c>
       <c r="R32" t="n">
-        <v>6734223</v>
+        <v>6734258</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,10 +3999,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216476</v>
+        <v>121216468</v>
       </c>
       <c r="B33" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511926</v>
+        <v>511953</v>
       </c>
       <c r="R33" t="n">
-        <v>6734268</v>
+        <v>6734306</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 50246-2024 artfynd.xlsx
+++ b/artfynd/A 50246-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216465</v>
+        <v>121216486</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511882</v>
+        <v>511930</v>
       </c>
       <c r="R2" t="n">
-        <v>6734284</v>
+        <v>6734223</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216489</v>
+        <v>121216455</v>
       </c>
       <c r="B3" t="n">
-        <v>100371</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511874</v>
+        <v>511912</v>
       </c>
       <c r="R3" t="n">
-        <v>6734258</v>
+        <v>6734222</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216455</v>
+        <v>121216464</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +891,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511912</v>
+        <v>511871</v>
       </c>
       <c r="R4" t="n">
-        <v>6734222</v>
+        <v>6734288</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216488</v>
+        <v>121216481</v>
       </c>
       <c r="B5" t="n">
-        <v>100371</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +1002,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511890</v>
+        <v>511892</v>
       </c>
       <c r="R5" t="n">
-        <v>6734232</v>
+        <v>6734294</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216481</v>
+        <v>121216483</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1141,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511892</v>
+        <v>511919</v>
       </c>
       <c r="R6" t="n">
-        <v>6734294</v>
+        <v>6734255</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216483</v>
+        <v>121216467</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1238,7 +1247,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1252,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511919</v>
+        <v>511936</v>
       </c>
       <c r="R7" t="n">
-        <v>6734255</v>
+        <v>6734297</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216486</v>
+        <v>121216473</v>
       </c>
       <c r="B8" t="n">
-        <v>100371</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,38 +1335,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511930</v>
+        <v>511888</v>
       </c>
       <c r="R8" t="n">
-        <v>6734223</v>
+        <v>6734296</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216461</v>
+        <v>121216462</v>
       </c>
       <c r="B9" t="n">
-        <v>91160</v>
+        <v>91006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,25 +1446,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1456,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511887</v>
+        <v>511910</v>
       </c>
       <c r="R9" t="n">
-        <v>6734253</v>
+        <v>6734222</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216463</v>
+        <v>121216468</v>
       </c>
       <c r="B10" t="n">
-        <v>91006</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1530,38 +1548,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511882</v>
+        <v>511953</v>
       </c>
       <c r="R10" t="n">
-        <v>6734252</v>
+        <v>6734306</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1647,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216474</v>
+        <v>121216476</v>
       </c>
       <c r="B11" t="n">
         <v>98105</v>
@@ -1655,7 +1682,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1669,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511908</v>
+        <v>511926</v>
       </c>
       <c r="R11" t="n">
-        <v>6734282</v>
+        <v>6734268</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216456</v>
+        <v>121216487</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
+        <v>100371</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,25 +1770,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511887</v>
+        <v>511896</v>
       </c>
       <c r="R12" t="n">
-        <v>6734253</v>
+        <v>6734236</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,7 +1860,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216466</v>
+        <v>121216471</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1868,7 +1895,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1882,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511896</v>
+        <v>511918</v>
       </c>
       <c r="R13" t="n">
-        <v>6734295</v>
+        <v>6734292</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216487</v>
+        <v>121216480</v>
       </c>
       <c r="B14" t="n">
-        <v>100371</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,38 +1983,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511896</v>
+        <v>511859</v>
       </c>
       <c r="R14" t="n">
-        <v>6734236</v>
+        <v>6734287</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2082,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216471</v>
+        <v>121216465</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2081,7 +2117,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2095,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511918</v>
+        <v>511882</v>
       </c>
       <c r="R15" t="n">
-        <v>6734292</v>
+        <v>6734284</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216454</v>
+        <v>121216461</v>
       </c>
       <c r="B16" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,25 +2205,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2197,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511885</v>
+        <v>511887</v>
       </c>
       <c r="R16" t="n">
-        <v>6734256</v>
+        <v>6734253</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216477</v>
+        <v>121216490</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,47 +2307,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511874</v>
+        <v>511875</v>
       </c>
       <c r="R17" t="n">
-        <v>6734290</v>
+        <v>6734249</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216476</v>
+        <v>121216463</v>
       </c>
       <c r="B18" t="n">
-        <v>98105</v>
+        <v>91006</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2382,47 +2409,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511926</v>
+        <v>511882</v>
       </c>
       <c r="R18" t="n">
-        <v>6734268</v>
+        <v>6734252</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216482</v>
+        <v>121216478</v>
       </c>
       <c r="B20" t="n">
         <v>98105</v>
@@ -2618,7 +2636,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2632,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511946</v>
+        <v>511932</v>
       </c>
       <c r="R20" t="n">
-        <v>6734303</v>
+        <v>6734295</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216490</v>
+        <v>121216454</v>
       </c>
       <c r="B21" t="n">
-        <v>100371</v>
+        <v>90720</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2724,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511875</v>
+        <v>511885</v>
       </c>
       <c r="R21" t="n">
-        <v>6734249</v>
+        <v>6734256</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2796,7 +2814,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216464</v>
+        <v>121216475</v>
       </c>
       <c r="B22" t="n">
         <v>98105</v>
@@ -2831,7 +2849,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2845,10 +2863,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511871</v>
+        <v>511912</v>
       </c>
       <c r="R22" t="n">
-        <v>6734288</v>
+        <v>6734269</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2925,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216472</v>
+        <v>121216469</v>
       </c>
       <c r="B23" t="n">
         <v>98105</v>
@@ -2942,7 +2960,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2956,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511926</v>
+        <v>511918</v>
       </c>
       <c r="R23" t="n">
-        <v>6734295</v>
+        <v>6734258</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,10 +3036,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216485</v>
+        <v>121216456</v>
       </c>
       <c r="B24" t="n">
-        <v>100371</v>
+        <v>90720</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,25 +3048,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3058,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511856</v>
+        <v>511887</v>
       </c>
       <c r="R24" t="n">
-        <v>6734258</v>
+        <v>6734253</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,10 +3138,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216462</v>
+        <v>121216474</v>
       </c>
       <c r="B25" t="n">
-        <v>91006</v>
+        <v>98105</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,38 +3150,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511910</v>
+        <v>511908</v>
       </c>
       <c r="R25" t="n">
-        <v>6734222</v>
+        <v>6734282</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,7 +3249,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216475</v>
+        <v>121216472</v>
       </c>
       <c r="B26" t="n">
         <v>98105</v>
@@ -3271,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511912</v>
+        <v>511926</v>
       </c>
       <c r="R26" t="n">
-        <v>6734269</v>
+        <v>6734295</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,7 +3360,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216467</v>
+        <v>121216477</v>
       </c>
       <c r="B27" t="n">
         <v>98105</v>
@@ -3368,7 +3395,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3382,10 +3409,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511936</v>
+        <v>511874</v>
       </c>
       <c r="R27" t="n">
-        <v>6734297</v>
+        <v>6734290</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216473</v>
+        <v>121216489</v>
       </c>
       <c r="B28" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,47 +3483,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511888</v>
+        <v>511874</v>
       </c>
       <c r="R28" t="n">
-        <v>6734296</v>
+        <v>6734258</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3555,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216480</v>
+        <v>121216488</v>
       </c>
       <c r="B29" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3567,47 +3585,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511859</v>
+        <v>511890</v>
       </c>
       <c r="R29" t="n">
-        <v>6734287</v>
+        <v>6734232</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3666,7 +3675,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216479</v>
+        <v>121216466</v>
       </c>
       <c r="B30" t="n">
         <v>98105</v>
@@ -3701,7 +3710,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3715,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511944</v>
+        <v>511896</v>
       </c>
       <c r="R30" t="n">
-        <v>6734302</v>
+        <v>6734295</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3777,7 +3786,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216478</v>
+        <v>121216479</v>
       </c>
       <c r="B31" t="n">
         <v>98105</v>
@@ -3826,10 +3835,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511932</v>
+        <v>511944</v>
       </c>
       <c r="R31" t="n">
-        <v>6734295</v>
+        <v>6734302</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,7 +3897,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216469</v>
+        <v>121216482</v>
       </c>
       <c r="B32" t="n">
         <v>98105</v>
@@ -3923,7 +3932,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3937,10 +3946,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511918</v>
+        <v>511946</v>
       </c>
       <c r="R32" t="n">
-        <v>6734258</v>
+        <v>6734303</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3999,10 +4008,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216468</v>
+        <v>121216485</v>
       </c>
       <c r="B33" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4011,47 +4020,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långrö, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511953</v>
+        <v>511856</v>
       </c>
       <c r="R33" t="n">
-        <v>6734306</v>
+        <v>6734258</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
